--- a/public/data/db-source/folder.xlsx
+++ b/public/data/db-source/folder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61895C4B-315A-AF4A-B96F-EDB6C50C64CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F76DBAF-2908-794E-AD8E-528EC87CCA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="500" windowWidth="26720" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="600" windowWidth="26720" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="322">
   <si>
     <t>id</t>
   </si>
@@ -977,6 +977,15 @@
   </si>
   <si>
     <t>pop-com-1, pdf_online</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>nomenclature</t>
+  </si>
+  <si>
+    <t>domaine</t>
   </si>
 </sst>
 </file>
@@ -1046,15 +1055,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}" name="Tableau1" displayName="Tableau1" ref="A1:S26" totalsRowShown="0">
-  <autoFilter ref="A1:S26" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}" name="Tableau1" displayName="Tableau1" ref="A1:T26" totalsRowShown="0">
+  <autoFilter ref="A1:T26" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}"/>
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{09DA0DB8-9D44-0745-A92C-DF1C35CD9EBE}" name="id"/>
     <tableColumn id="2" xr3:uid="{21E98347-F74D-DB40-8A51-7D5294DE73EA}" name="parent_id"/>
     <tableColumn id="3" xr3:uid="{E4E9BDF4-CE25-694D-BE63-C890319027E7}" name="owner_id"/>
     <tableColumn id="4" xr3:uid="{C6DCB782-453E-0E44-8BD2-1A038F424D58}" name="manager_id"/>
     <tableColumn id="5" xr3:uid="{05630E2D-DD2A-DC47-8BF6-C695A69BA271}" name="name"/>
     <tableColumn id="6" xr3:uid="{B36D989D-272D-3540-87E5-C216F0DDE856}" name="description"/>
+    <tableColumn id="20" xr3:uid="{43F330F2-50F9-5244-91AC-D6398C5D5F79}" name="type"/>
     <tableColumn id="7" xr3:uid="{99F6A068-71AF-D84C-8D8A-77A929819CBD}" name="start_date"/>
     <tableColumn id="8" xr3:uid="{BEE703A4-8F5F-C041-BB42-6D61F673A020}" name="end_date"/>
     <tableColumn id="9" xr3:uid="{F4FD44D2-A43C-B444-8FF8-40322366BA8A}" name="localisation"/>
@@ -1360,30 +1370,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.5" customWidth="1"/>
-    <col min="6" max="6" width="36.5" customWidth="1"/>
-    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="36.5" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1403,46 +1413,49 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>319</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>100</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>98</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1459,41 +1472,44 @@
         <v>61</v>
       </c>
       <c r="G2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H2" t="s">
         <v>103</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>104</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>162</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>163</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>164</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>165</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>140</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" t="s">
+      <c r="O2" s="1"/>
+      <c r="P2" t="s">
         <v>191</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>192</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>193</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1513,40 +1529,43 @@
         <v>67</v>
       </c>
       <c r="G3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H3" t="s">
         <v>105</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>106</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>166</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>167</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>164</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>168</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>141</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>194</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>195</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1566,38 +1585,41 @@
         <v>68</v>
       </c>
       <c r="G4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H4" t="s">
         <v>107</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>169</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>170</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>171</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>165</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>142</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" t="s">
+      <c r="O4" s="1"/>
+      <c r="P4" t="s">
         <v>197</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>198</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>199</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1617,41 +1639,44 @@
         <v>69</v>
       </c>
       <c r="G5" t="s">
+        <v>321</v>
+      </c>
+      <c r="H5" t="s">
         <v>108</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>109</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>172</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>170</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>173</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>174</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>143</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="O5" t="s">
+      <c r="O5" s="1"/>
+      <c r="P5" t="s">
         <v>200</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>201</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>202</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1670,41 +1695,44 @@
       <c r="F6" t="s">
         <v>70</v>
       </c>
-      <c r="H6" t="s">
+      <c r="G6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I6" t="s">
         <v>110</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>169</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>175</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>176</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>177</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>144</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>203</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>204</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>205</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1723,39 +1751,42 @@
       <c r="F7" t="s">
         <v>71</v>
       </c>
-      <c r="I7" t="s">
+      <c r="G7" t="s">
+        <v>321</v>
+      </c>
+      <c r="J7" t="s">
         <v>178</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>170</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>179</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>180</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>145</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" t="s">
+      <c r="O7" s="1"/>
+      <c r="P7" t="s">
         <v>206</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>207</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>208</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>295</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1772,41 +1803,44 @@
         <v>72</v>
       </c>
       <c r="G8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H8" t="s">
         <v>111</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>178</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>167</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>181</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>177</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>146</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" t="s">
+      <c r="O8" s="1"/>
+      <c r="P8" t="s">
         <v>209</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>210</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>211</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>296</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1826,41 +1860,44 @@
         <v>73</v>
       </c>
       <c r="G9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H9" t="s">
         <v>112</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>113</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>182</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>167</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>164</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>165</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>147</v>
       </c>
-      <c r="N9" s="1"/>
-      <c r="O9" t="s">
+      <c r="O9" s="1"/>
+      <c r="P9" t="s">
         <v>212</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>213</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>214</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1877,35 +1914,38 @@
         <v>74</v>
       </c>
       <c r="G10" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10" t="s">
         <v>114</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>166</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>183</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>176</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>165</v>
       </c>
-      <c r="N10" s="1"/>
-      <c r="O10" t="s">
+      <c r="O10" s="1"/>
+      <c r="P10" t="s">
         <v>215</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>216</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>217</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1925,35 +1965,38 @@
         <v>75</v>
       </c>
       <c r="G11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H11" t="s">
         <v>115</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>184</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>167</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>171</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>180</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>148</v>
       </c>
-      <c r="N11" s="1"/>
-      <c r="O11" t="s">
+      <c r="O11" s="1"/>
+      <c r="P11" t="s">
         <v>218</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>219</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1973,44 +2016,47 @@
         <v>76</v>
       </c>
       <c r="G12" t="s">
+        <v>321</v>
+      </c>
+      <c r="H12" t="s">
         <v>116</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>117</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>169</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>185</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>181</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>174</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>149</v>
       </c>
-      <c r="N12" s="1"/>
-      <c r="O12" t="s">
+      <c r="O12" s="1"/>
+      <c r="P12" t="s">
         <v>221</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>222</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>223</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>299</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2024,40 +2070,43 @@
         <v>77</v>
       </c>
       <c r="G13" t="s">
+        <v>321</v>
+      </c>
+      <c r="H13" t="s">
         <v>118</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>186</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>170</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>187</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>168</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>150</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>224</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>225</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>226</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -2077,44 +2126,47 @@
         <v>78</v>
       </c>
       <c r="G14" t="s">
+        <v>321</v>
+      </c>
+      <c r="H14" t="s">
         <v>119</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>120</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>188</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>163</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>173</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>168</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>151</v>
       </c>
-      <c r="N14" s="1"/>
-      <c r="O14" t="s">
+      <c r="O14" s="1"/>
+      <c r="P14" t="s">
         <v>227</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>228</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>229</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>301</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2134,41 +2186,44 @@
         <v>79</v>
       </c>
       <c r="G15" t="s">
+        <v>321</v>
+      </c>
+      <c r="H15" t="s">
         <v>121</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>122</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>169</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>185</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>173</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>174</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>152</v>
       </c>
-      <c r="N15" s="1"/>
-      <c r="O15" t="s">
+      <c r="O15" s="1"/>
+      <c r="P15" t="s">
         <v>230</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>231</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>232</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2188,41 +2243,44 @@
         <v>80</v>
       </c>
       <c r="G16" t="s">
+        <v>321</v>
+      </c>
+      <c r="H16" t="s">
         <v>123</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>124</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>166</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>185</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>171</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>168</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>153</v>
       </c>
-      <c r="N16" s="1"/>
-      <c r="O16" t="s">
+      <c r="O16" s="1"/>
+      <c r="P16" t="s">
         <v>233</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>234</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>235</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -2242,35 +2300,38 @@
         <v>81</v>
       </c>
       <c r="G17" t="s">
+        <v>321</v>
+      </c>
+      <c r="H17" t="s">
         <v>125</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>186</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>175</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>176</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>174</v>
       </c>
-      <c r="N17" s="1"/>
-      <c r="O17" t="s">
+      <c r="O17" s="1"/>
+      <c r="P17" t="s">
         <v>236</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>237</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>238</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -2290,44 +2351,47 @@
         <v>82</v>
       </c>
       <c r="G18" t="s">
+        <v>321</v>
+      </c>
+      <c r="H18" t="s">
         <v>126</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>127</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>178</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>185</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>173</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>177</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>154</v>
       </c>
-      <c r="N18" s="1"/>
-      <c r="O18" t="s">
+      <c r="O18" s="1"/>
+      <c r="P18" t="s">
         <v>239</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>240</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>241</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>305</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2347,46 +2411,49 @@
         <v>83</v>
       </c>
       <c r="G19" t="s">
+        <v>321</v>
+      </c>
+      <c r="H19" t="s">
         <v>128</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>129</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>184</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>167</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>173</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>177</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>155</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>242</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>243</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>244</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>306</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -2406,35 +2473,38 @@
         <v>84</v>
       </c>
       <c r="G20" t="s">
+        <v>321</v>
+      </c>
+      <c r="H20" t="s">
         <v>130</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>189</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>167</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>173</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>180</v>
       </c>
-      <c r="N20" s="1"/>
-      <c r="O20" t="s">
+      <c r="O20" s="1"/>
+      <c r="P20" t="s">
         <v>245</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>246</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>247</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2454,41 +2524,44 @@
         <v>85</v>
       </c>
       <c r="G21" t="s">
+        <v>321</v>
+      </c>
+      <c r="H21" t="s">
         <v>131</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>132</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>186</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>170</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>181</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>165</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>156</v>
       </c>
-      <c r="N21" s="1"/>
-      <c r="O21" t="s">
+      <c r="O21" s="1"/>
+      <c r="P21" t="s">
         <v>248</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>249</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>250</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -2508,41 +2581,44 @@
         <v>86</v>
       </c>
       <c r="G22" t="s">
+        <v>321</v>
+      </c>
+      <c r="H22" t="s">
         <v>133</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>166</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>190</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>176</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>180</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>157</v>
       </c>
-      <c r="N22" s="1"/>
-      <c r="O22" t="s">
+      <c r="O22" s="1"/>
+      <c r="P22" t="s">
         <v>251</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>252</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>253</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>309</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -2562,38 +2638,41 @@
         <v>87</v>
       </c>
       <c r="G23" t="s">
+        <v>321</v>
+      </c>
+      <c r="H23" t="s">
         <v>107</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>134</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>162</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>167</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>181</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>177</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>158</v>
       </c>
-      <c r="N23" s="1"/>
-      <c r="O23" t="s">
+      <c r="O23" s="1"/>
+      <c r="P23" t="s">
         <v>254</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>255</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2613,41 +2692,44 @@
         <v>88</v>
       </c>
       <c r="G24" t="s">
+        <v>321</v>
+      </c>
+      <c r="H24" t="s">
         <v>135</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>136</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>162</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>183</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>187</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>165</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="1"/>
-      <c r="O24" t="s">
+      <c r="O24" s="1"/>
+      <c r="P24" t="s">
         <v>257</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>258</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>259</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -2666,42 +2748,42 @@
       <c r="F25" t="s">
         <v>64</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>137</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>138</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>178</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>175</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>164</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>177</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>160</v>
       </c>
-      <c r="N25" s="1"/>
-      <c r="O25" t="s">
+      <c r="O25" s="1"/>
+      <c r="P25" t="s">
         <v>260</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>261</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>262</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2720,37 +2802,37 @@
       <c r="F26" t="s">
         <v>65</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>139</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>172</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>167</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>173</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>165</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>161</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>263</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>264</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>265</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>312</v>
       </c>
     </row>

--- a/public/data/db-source/folder.xlsx
+++ b/public/data/db-source/folder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F76DBAF-2908-794E-AD8E-528EC87CCA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF21DDFE-8215-584B-9BCA-2BE56A193B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="600" windowWidth="26720" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="600" windowWidth="26720" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="323">
   <si>
     <t>id</t>
   </si>
@@ -349,9 +349,6 @@
     <t>2022/06/04</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>2020/10</t>
   </si>
   <si>
@@ -361,9 +358,6 @@
     <t>2023</t>
   </si>
   <si>
-    <t>2023/09</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -451,9 +445,6 @@
     <t>2018/08/20</t>
   </si>
   <si>
-    <t>2020/03/25</t>
-  </si>
-  <si>
     <t>2025/10/26</t>
   </si>
   <si>
@@ -478,9 +469,6 @@
     <t>2017/12/12</t>
   </si>
   <si>
-    <t>2011/03/02</t>
-  </si>
-  <si>
     <t>2025/01/22</t>
   </si>
   <si>
@@ -986,13 +974,28 @@
   </si>
   <si>
     <t>domaine</t>
+  </si>
+  <si>
+    <t>2029/09</t>
+  </si>
+  <si>
+    <t>2028/03</t>
+  </si>
+  <si>
+    <t>2026/03/25</t>
+  </si>
+  <si>
+    <t>2026/04/25</t>
+  </si>
+  <si>
+    <t>2026/04/20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1006,16 +1009,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1023,13 +1039,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1413,7 +1445,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -1463,7 +1495,7 @@
         <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -1472,7 +1504,7 @@
         <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H2" t="s">
         <v>103</v>
@@ -1481,32 +1513,32 @@
         <v>104</v>
       </c>
       <c r="J2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="Q2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="R2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="S2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
@@ -1517,10 +1549,10 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -1529,7 +1561,7 @@
         <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H3" t="s">
         <v>105</v>
@@ -1538,31 +1570,31 @@
         <v>106</v>
       </c>
       <c r="J3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" t="s">
         <v>164</v>
       </c>
-      <c r="M3" t="s">
-        <v>168</v>
-      </c>
       <c r="N3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Q3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="R3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
@@ -1573,7 +1605,7 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
@@ -1585,38 +1617,41 @@
         <v>68</v>
       </c>
       <c r="G4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H4" t="s">
         <v>107</v>
       </c>
+      <c r="I4" t="s">
+        <v>319</v>
+      </c>
       <c r="J4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="Q4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="R4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="S4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
@@ -1627,10 +1662,10 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -1639,41 +1674,41 @@
         <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H5" t="s">
         <v>108</v>
       </c>
-      <c r="I5" t="s">
-        <v>109</v>
+      <c r="I5">
+        <v>2028</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" t="s">
+        <v>169</v>
+      </c>
+      <c r="M5" t="s">
         <v>170</v>
       </c>
-      <c r="L5" t="s">
-        <v>173</v>
-      </c>
-      <c r="M5" t="s">
-        <v>174</v>
-      </c>
-      <c r="N5" t="s">
-        <v>143</v>
+      <c r="N5" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Q5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="R5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="S5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -1687,7 +1722,7 @@
         <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -1696,37 +1731,37 @@
         <v>70</v>
       </c>
       <c r="G6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="N6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="Q6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="R6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="T6" t="s">
         <v>102</v>
@@ -1740,10 +1775,10 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -1752,38 +1787,38 @@
         <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Q7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="R7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="S7" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="T7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
@@ -1803,41 +1838,41 @@
         <v>72</v>
       </c>
       <c r="G8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="N8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="R8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="S8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="T8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
@@ -1848,7 +1883,7 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -1860,41 +1895,41 @@
         <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I9" t="s">
-        <v>113</v>
+        <v>318</v>
       </c>
       <c r="J9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="R9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="S9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
@@ -1914,35 +1949,35 @@
         <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K10" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Q10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="R10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="S10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
@@ -1953,10 +1988,10 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D11" t="s">
         <v>271</v>
-      </c>
-      <c r="D11" t="s">
-        <v>275</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -1965,35 +2000,35 @@
         <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J11" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L11" t="s">
         <v>167</v>
       </c>
-      <c r="L11" t="s">
-        <v>171</v>
-      </c>
       <c r="M11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="R11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -2004,10 +2039,10 @@
         <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -2016,44 +2051,44 @@
         <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K12" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Q12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="R12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S12" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="T12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
@@ -2070,40 +2105,40 @@
         <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Q13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="R13" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="S13" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
@@ -2114,7 +2149,7 @@
         <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D14" t="s">
         <v>97</v>
@@ -2126,44 +2161,44 @@
         <v>78</v>
       </c>
       <c r="G14" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J14" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q14" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="R14" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="S14" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="T14" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
@@ -2177,7 +2212,7 @@
         <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E15" t="s">
         <v>41</v>
@@ -2186,41 +2221,41 @@
         <v>79</v>
       </c>
       <c r="G15" t="s">
+        <v>317</v>
+      </c>
+      <c r="H15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" t="s">
+        <v>120</v>
+      </c>
+      <c r="J15" t="s">
+        <v>165</v>
+      </c>
+      <c r="K15" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" t="s">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s">
+        <v>170</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="H15" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" t="s">
-        <v>169</v>
-      </c>
-      <c r="K15" t="s">
-        <v>185</v>
-      </c>
-      <c r="L15" t="s">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s">
-        <v>152</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Q15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="R15" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="S15" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
@@ -2231,10 +2266,10 @@
         <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E16" t="s">
         <v>43</v>
@@ -2243,41 +2278,41 @@
         <v>80</v>
       </c>
       <c r="G16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="R16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="S16" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
@@ -2288,10 +2323,10 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D17" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -2300,35 +2335,38 @@
         <v>81</v>
       </c>
       <c r="G17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M17" t="s">
-        <v>174</v>
+        <v>170</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="Q17" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="R17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S17" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -2339,10 +2377,10 @@
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D18" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E18" t="s">
         <v>47</v>
@@ -2351,44 +2389,44 @@
         <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K18" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L18" t="s">
+        <v>169</v>
+      </c>
+      <c r="M18" t="s">
         <v>173</v>
       </c>
-      <c r="M18" t="s">
-        <v>177</v>
-      </c>
       <c r="N18" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O18" s="1"/>
       <c r="P18" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Q18" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R18" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="S18" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="T18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
@@ -2399,10 +2437,10 @@
         <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E19" t="s">
         <v>49</v>
@@ -2411,46 +2449,46 @@
         <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J19" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K19" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M19" t="s">
         <v>173</v>
       </c>
-      <c r="M19" t="s">
-        <v>177</v>
-      </c>
       <c r="N19" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Q19" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="R19" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="S19" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="T19" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
@@ -2461,10 +2499,10 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E20" t="s">
         <v>51</v>
@@ -2473,35 +2511,35 @@
         <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J20" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K20" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L20" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Q20" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R20" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="S20" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
@@ -2512,10 +2550,10 @@
         <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D21" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E21" t="s">
         <v>53</v>
@@ -2524,41 +2562,41 @@
         <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J21" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K21" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L21" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M21" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="Q21" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R21" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="S21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -2569,10 +2607,10 @@
         <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D22" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
@@ -2581,41 +2619,41 @@
         <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J22" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K22" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s">
+        <v>172</v>
+      </c>
+      <c r="M22" t="s">
         <v>176</v>
       </c>
-      <c r="M22" t="s">
-        <v>180</v>
-      </c>
       <c r="N22" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Q22" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="R22" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="S22" t="s">
+        <v>305</v>
+      </c>
+      <c r="T22" t="s">
         <v>309</v>
-      </c>
-      <c r="T22" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
@@ -2626,10 +2664,10 @@
         <v>60</v>
       </c>
       <c r="C23" t="s">
+        <v>281</v>
+      </c>
+      <c r="D23" t="s">
         <v>285</v>
-      </c>
-      <c r="D23" t="s">
-        <v>289</v>
       </c>
       <c r="E23" t="s">
         <v>57</v>
@@ -2638,38 +2676,38 @@
         <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H23" t="s">
         <v>107</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J23" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K23" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M23" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="N23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="Q23" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="R23" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
@@ -2680,10 +2718,10 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E24" t="s">
         <v>59</v>
@@ -2692,41 +2730,41 @@
         <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K24" t="s">
+        <v>179</v>
+      </c>
+      <c r="L24" t="s">
         <v>183</v>
       </c>
-      <c r="L24" t="s">
-        <v>187</v>
-      </c>
       <c r="M24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Q24" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R24" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -2740,7 +2778,7 @@
         <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
@@ -2749,38 +2787,38 @@
         <v>64</v>
       </c>
       <c r="H25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J25" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K25" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="N25" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O25" s="1"/>
       <c r="P25" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Q25" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="R25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="S25" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
@@ -2794,7 +2832,7 @@
         <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
         <v>90</v>
@@ -2803,37 +2841,37 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J26" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K26" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L26" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="Q26" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="R26" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="S26" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/db-source/folder.xlsx
+++ b/public/data/db-source/folder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF21DDFE-8215-584B-9BCA-2BE56A193B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCF4C5F-9B6C-9E43-B4B5-BDC682365742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2080" yWindow="600" windowWidth="26720" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="326">
   <si>
     <t>id</t>
   </si>
@@ -989,6 +989,15 @@
   </si>
   <si>
     <t>2026/04/20</t>
+  </si>
+  <si>
+    <t>license</t>
+  </si>
+  <si>
+    <t>Licence Ouverte / Open Licence v2.0</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by/4.0/</t>
   </si>
 </sst>
 </file>
@@ -1058,15 +1067,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -1087,9 +1100,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}" name="Tableau1" displayName="Tableau1" ref="A1:T26" totalsRowShown="0">
-  <autoFilter ref="A1:T26" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}" name="Tableau1" displayName="Tableau1" ref="A1:U26" totalsRowShown="0">
+  <autoFilter ref="A1:U26" xr:uid="{C08C76FB-17A0-4B45-8906-D499EF0568E9}"/>
+  <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{09DA0DB8-9D44-0745-A92C-DF1C35CD9EBE}" name="id"/>
     <tableColumn id="2" xr3:uid="{21E98347-F74D-DB40-8A51-7D5294DE73EA}" name="parent_id"/>
     <tableColumn id="3" xr3:uid="{E4E9BDF4-CE25-694D-BE63-C890319027E7}" name="owner_id"/>
@@ -1103,8 +1116,9 @@
     <tableColumn id="10" xr3:uid="{0602EF7E-E665-9A45-B5A6-113DE6426605}" name="survey_type"/>
     <tableColumn id="11" xr3:uid="{4A0B91C2-9825-EC4D-840F-587D66E826AC}" name="delivery_format"/>
     <tableColumn id="12" xr3:uid="{04411BD8-781F-244C-A2BE-8F3FEF5CE025}" name="updating_each"/>
-    <tableColumn id="13" xr3:uid="{3A4CF3CE-FE05-A74B-A25A-998DA66B76EB}" name="last_update_date" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{1EF57530-A605-664A-A98A-2D48430BC346}" name="no_more_update" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{3A4CF3CE-FE05-A74B-A25A-998DA66B76EB}" name="last_update_date" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{1EF57530-A605-664A-A98A-2D48430BC346}" name="no_more_update" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{C6613132-2B62-B44E-9242-559A61EA9568}" name="license" dataDxfId="0"/>
     <tableColumn id="14" xr3:uid="{796DA115-F354-914F-88E3-19F47C8A40A1}" name="metadata_path"/>
     <tableColumn id="15" xr3:uid="{FA92769D-F3F4-0549-91ED-42BA1FB808FB}" name="data_path"/>
     <tableColumn id="16" xr3:uid="{97EA7C5B-D3BE-A440-A583-D4CDA21A8E2A}" name="git_code"/>
@@ -1402,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -1417,15 +1431,15 @@
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1472,22 +1486,25 @@
         <v>100</v>
       </c>
       <c r="P1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>98</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1528,20 +1545,21 @@
         <v>138</v>
       </c>
       <c r="O2" s="1"/>
-      <c r="P2" t="s">
+      <c r="P2" s="1"/>
+      <c r="Q2" t="s">
         <v>187</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>188</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>189</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1587,17 +1605,18 @@
       <c r="O3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="1"/>
+      <c r="Q3" t="s">
         <v>190</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>191</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1641,20 +1660,23 @@
         <v>140</v>
       </c>
       <c r="O4" s="1"/>
-      <c r="P4" t="s">
+      <c r="P4" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q4" t="s">
         <v>193</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>194</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>195</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1698,20 +1720,21 @@
         <v>320</v>
       </c>
       <c r="O5" s="1"/>
-      <c r="P5" t="s">
+      <c r="P5" s="1"/>
+      <c r="Q5" t="s">
         <v>196</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>197</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>198</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1754,20 +1777,21 @@
       <c r="O6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="1"/>
+      <c r="Q6" t="s">
         <v>199</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>200</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>201</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1805,23 +1829,24 @@
         <v>142</v>
       </c>
       <c r="O7" s="1"/>
-      <c r="P7" t="s">
+      <c r="P7" s="1"/>
+      <c r="Q7" t="s">
         <v>202</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>203</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>204</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>291</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1859,23 +1884,26 @@
         <v>143</v>
       </c>
       <c r="O8" s="1"/>
-      <c r="P8" t="s">
+      <c r="P8" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q8" t="s">
         <v>205</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>206</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>207</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>292</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1919,20 +1947,21 @@
         <v>144</v>
       </c>
       <c r="O9" s="1"/>
-      <c r="P9" t="s">
+      <c r="P9" s="1"/>
+      <c r="Q9" t="s">
         <v>208</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>209</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>210</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1967,20 +1996,21 @@
         <v>161</v>
       </c>
       <c r="O10" s="1"/>
-      <c r="P10" t="s">
+      <c r="P10" s="1"/>
+      <c r="Q10" t="s">
         <v>211</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>212</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>213</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2021,17 +2051,18 @@
         <v>145</v>
       </c>
       <c r="O11" s="1"/>
-      <c r="P11" t="s">
+      <c r="P11" s="1"/>
+      <c r="Q11" t="s">
         <v>214</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>215</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -2075,23 +2106,24 @@
         <v>146</v>
       </c>
       <c r="O12" s="1"/>
-      <c r="P12" t="s">
+      <c r="P12" s="1"/>
+      <c r="Q12" t="s">
         <v>217</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>218</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>219</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>295</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2128,20 +2160,21 @@
       <c r="O13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="1"/>
+      <c r="Q13" t="s">
         <v>220</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>221</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>222</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -2185,23 +2218,24 @@
         <v>148</v>
       </c>
       <c r="O14" s="1"/>
-      <c r="P14" t="s">
+      <c r="P14" s="1"/>
+      <c r="Q14" t="s">
         <v>223</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>224</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>225</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>297</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2245,20 +2279,21 @@
         <v>321</v>
       </c>
       <c r="O15" s="1"/>
-      <c r="P15" t="s">
+      <c r="P15" s="1"/>
+      <c r="Q15" t="s">
         <v>226</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>227</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>228</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2302,20 +2337,21 @@
         <v>149</v>
       </c>
       <c r="O16" s="1"/>
-      <c r="P16" t="s">
+      <c r="P16" s="1"/>
+      <c r="Q16" t="s">
         <v>229</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>230</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>231</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -2356,20 +2392,23 @@
         <v>322</v>
       </c>
       <c r="O17" s="1"/>
-      <c r="P17" t="s">
+      <c r="P17" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q17" t="s">
         <v>232</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>233</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>234</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -2413,23 +2452,24 @@
         <v>150</v>
       </c>
       <c r="O18" s="1"/>
-      <c r="P18" t="s">
+      <c r="P18" s="1"/>
+      <c r="Q18" t="s">
         <v>235</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>236</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>237</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>301</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2475,23 +2515,24 @@
       <c r="O19" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="1"/>
+      <c r="Q19" t="s">
         <v>238</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>239</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>240</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>302</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -2529,20 +2570,21 @@
         <v>176</v>
       </c>
       <c r="O20" s="1"/>
-      <c r="P20" t="s">
+      <c r="P20" s="1"/>
+      <c r="Q20" t="s">
         <v>241</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>242</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>243</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2586,20 +2628,21 @@
         <v>152</v>
       </c>
       <c r="O21" s="1"/>
-      <c r="P21" t="s">
+      <c r="P21" s="1"/>
+      <c r="Q21" t="s">
         <v>244</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>245</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>246</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -2640,23 +2683,26 @@
         <v>153</v>
       </c>
       <c r="O22" s="1"/>
-      <c r="P22" t="s">
+      <c r="P22" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q22" t="s">
         <v>247</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>248</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>249</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>305</v>
       </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -2700,17 +2746,18 @@
         <v>154</v>
       </c>
       <c r="O23" s="1"/>
-      <c r="P23" t="s">
+      <c r="P23" s="1"/>
+      <c r="Q23" t="s">
         <v>250</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>251</v>
       </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2754,20 +2801,21 @@
         <v>155</v>
       </c>
       <c r="O24" s="1"/>
-      <c r="P24" t="s">
+      <c r="P24" s="1"/>
+      <c r="Q24" t="s">
         <v>253</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>254</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>255</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -2808,20 +2856,21 @@
         <v>156</v>
       </c>
       <c r="O25" s="1"/>
-      <c r="P25" t="s">
+      <c r="P25" s="1"/>
+      <c r="Q25" t="s">
         <v>256</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>257</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>258</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2861,16 +2910,17 @@
       <c r="O26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P26" t="s">
+      <c r="P26" s="1"/>
+      <c r="Q26" t="s">
         <v>259</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>260</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>261</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>308</v>
       </c>
     </row>
